--- a/Tabelas/criterios_por_tipo.xlsx
+++ b/Tabelas/criterios_por_tipo.xlsx
@@ -515,46 +515,46 @@
         <v>0.36</v>
       </c>
       <c r="C2" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="D2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>84.97</v>
+        <v>85.87</v>
       </c>
       <c r="F2" t="n">
-        <v>55.89</v>
+        <v>57.56</v>
       </c>
       <c r="G2" t="n">
-        <v>95.84999999999999</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>89.02</v>
+        <v>89.63</v>
       </c>
       <c r="I2" t="n">
-        <v>55.56</v>
+        <v>52.57</v>
       </c>
       <c r="J2" t="n">
-        <v>46.47</v>
+        <v>46.42</v>
       </c>
       <c r="K2" t="n">
-        <v>19.76</v>
+        <v>21.43</v>
       </c>
       <c r="L2" t="n">
-        <v>9.26</v>
+        <v>9.81</v>
       </c>
       <c r="M2" t="n">
-        <v>63.8</v>
+        <v>64.02</v>
       </c>
       <c r="N2" t="n">
-        <v>16.72</v>
+        <v>19.44</v>
       </c>
       <c r="O2" t="n">
-        <v>56.57</v>
+        <v>54.59</v>
       </c>
       <c r="P2" t="n">
-        <v>98.17</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -567,46 +567,46 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>27.33</v>
+        <v>27.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="E3" t="n">
-        <v>90.86</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>49.42</v>
+        <v>49.56</v>
       </c>
       <c r="G3" t="n">
-        <v>98.83</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>93.68000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>53.79</v>
+        <v>53.53</v>
       </c>
       <c r="J3" t="n">
-        <v>27.14</v>
+        <v>27.11</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>25.07</v>
       </c>
       <c r="L3" t="n">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="M3" t="n">
-        <v>36.38</v>
+        <v>36.59</v>
       </c>
       <c r="N3" t="n">
-        <v>12.06</v>
+        <v>12.29</v>
       </c>
       <c r="O3" t="n">
-        <v>53.6</v>
+        <v>53.53</v>
       </c>
       <c r="P3" t="n">
-        <v>93.39</v>
+        <v>93.31999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -619,46 +619,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5.88</v>
+        <v>27.14</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>94.12</v>
+        <v>97.14</v>
       </c>
       <c r="F4" t="n">
-        <v>85.29000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>97.06</v>
+        <v>97.14</v>
       </c>
       <c r="I4" t="n">
-        <v>20.59</v>
+        <v>15.71</v>
       </c>
       <c r="J4" t="n">
-        <v>67.65000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="K4" t="n">
-        <v>52.94</v>
+        <v>54.29</v>
       </c>
       <c r="L4" t="n">
-        <v>32.35</v>
+        <v>21.43</v>
       </c>
       <c r="M4" t="n">
-        <v>82.34999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>58.82</v>
+        <v>44.29</v>
       </c>
       <c r="O4" t="n">
-        <v>20.59</v>
+        <v>24.29</v>
       </c>
       <c r="P4" t="n">
-        <v>88.23999999999999</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="5">
